--- a/artfynd/A 34227-2026 artfynd.xlsx
+++ b/artfynd/A 34227-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,57 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117700148</v>
+        <v>136893919</v>
       </c>
       <c r="B2" t="n">
-        <v>8455</v>
+        <v>93449</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skallerudbergen, Nrk</t>
+          <t>Lillsjön, Lillsjön, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505312</v>
+        <v>505316</v>
       </c>
       <c r="R2" t="n">
-        <v>6545020</v>
+        <v>6545009</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,34 +769,38 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Häll- och blockskog</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117700148</t>
+          <t>https://artportalen.se/Sighting/136893919</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117700121</v>
+        <v>117700148</v>
       </c>
       <c r="B3" t="n">
-        <v>8444</v>
+        <v>8455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505177</v>
+        <v>505312</v>
       </c>
       <c r="R3" t="n">
-        <v>6545105</v>
+        <v>6545020</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -898,16 +903,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117700121</t>
+          <t>https://artportalen.se/Sighting/117700148</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117700142</v>
+        <v>117700121</v>
       </c>
       <c r="B4" t="n">
-        <v>40300</v>
+        <v>8444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>214803</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505276</v>
+        <v>505177</v>
       </c>
       <c r="R4" t="n">
-        <v>6545064</v>
+        <v>6545105</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1009,6 +1014,118 @@
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117700121</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>117700142</v>
+      </c>
+      <c r="B5" t="n">
+        <v>40300</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>214803</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dolkstekelsglasvinge</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Synanthedon scoliaeformis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Borkhausen, 1789)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skallerudbergen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>505276</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6545064</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/117700142</t>
         </is>
@@ -1019,6 +1136,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34227-2026 artfynd.xlsx
+++ b/artfynd/A 34227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136893919</v>
       </c>
       <c r="B2" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34227-2026 artfynd.xlsx
+++ b/artfynd/A 34227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136893919</v>
       </c>
       <c r="B2" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34227-2026 artfynd.xlsx
+++ b/artfynd/A 34227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136893919</v>
       </c>
       <c r="B2" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34227-2026 artfynd.xlsx
+++ b/artfynd/A 34227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136893919</v>
       </c>
       <c r="B2" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34227-2026 artfynd.xlsx
+++ b/artfynd/A 34227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136893919</v>
       </c>
       <c r="B2" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34227-2026 artfynd.xlsx
+++ b/artfynd/A 34227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136893919</v>
       </c>
       <c r="B2" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34227-2026 artfynd.xlsx
+++ b/artfynd/A 34227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136893919</v>
       </c>
       <c r="B2" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34227-2026 artfynd.xlsx
+++ b/artfynd/A 34227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136893919</v>
       </c>
       <c r="B2" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34227-2026 artfynd.xlsx
+++ b/artfynd/A 34227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136893919</v>
       </c>
       <c r="B2" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34227-2026 artfynd.xlsx
+++ b/artfynd/A 34227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136893919</v>
       </c>
       <c r="B2" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34227-2026 artfynd.xlsx
+++ b/artfynd/A 34227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136893919</v>
       </c>
       <c r="B2" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34227-2026 artfynd.xlsx
+++ b/artfynd/A 34227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136893919</v>
       </c>
       <c r="B2" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34227-2026 artfynd.xlsx
+++ b/artfynd/A 34227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136893919</v>
       </c>
       <c r="B2" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34227-2026 artfynd.xlsx
+++ b/artfynd/A 34227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136893919</v>
       </c>
       <c r="B2" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34227-2026 artfynd.xlsx
+++ b/artfynd/A 34227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136893919</v>
       </c>
       <c r="B2" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34227-2026 artfynd.xlsx
+++ b/artfynd/A 34227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136893919</v>
       </c>
       <c r="B2" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34227-2026 artfynd.xlsx
+++ b/artfynd/A 34227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136893919</v>
       </c>
       <c r="B2" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
